--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261022.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261022.xlsx
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.7196907216494846</v>
+        <v>0.7222680412371134</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.08243298969072158</v>
+        <v>0.08501030927835046</v>
       </c>
     </row>
     <row r="8">
@@ -3860,118 +3860,118 @@
     <row r="3">
       <c r="A3" s="19" t="inlineStr">
         <is>
-          <t>P9 意見聴取</t>
+          <t>P4 調査結果の反映</t>
         </is>
       </c>
       <c r="B3" s="20" t="inlineStr">
         <is>
-          <t>9-1</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="C3" s="19" t="inlineStr">
         <is>
-          <t>協議会の開催回数・時期の確定</t>
+          <t>個票によるクロス集計</t>
         </is>
       </c>
       <c r="D3" s="20" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E3" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F3" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="G3" s="25" t="inlineStr">
-        <is>
-          <t>要対応</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G3" s="26" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
         </is>
       </c>
       <c r="H3" s="32" t="n">
         <v>0</v>
       </c>
       <c r="I3" s="32" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="J3" s="32" t="n">
-        <v>-100</v>
+        <v>-85</v>
       </c>
       <c r="K3" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="25" t="inlineStr">
-        <is>
-          <t>期限超過（2か月）</t>
+        <v>3</v>
+      </c>
+      <c r="L3" s="26" t="inlineStr">
+        <is>
+          <t>遅れ</t>
         </is>
       </c>
       <c r="M3" s="19" t="inlineStr">
         <is>
-          <t>**町との協議（依頼票C4）。これが決まらないと工程が引けない**</t>
+          <t>**令和7年度調査の個票データ（依頼票H16）。地区情報の有無も要確認**</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="19" t="inlineStr">
         <is>
-          <t>P4 調査結果の反映</t>
+          <t>P9 意見聴取</t>
         </is>
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="C4" s="19" t="inlineStr">
         <is>
-          <t>個票によるクロス集計</t>
+          <t>協議会 第1回（第9期の評価・調査結果）</t>
         </is>
       </c>
       <c r="D4" s="20" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E4" s="20" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="F4" s="20" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="G4" s="26" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
+      <c r="G4" s="25" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="H4" s="32" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I4" s="32" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="J4" s="32" t="n">
-        <v>-85</v>
+        <v>-50</v>
       </c>
       <c r="K4" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" s="26" t="inlineStr">
-        <is>
-          <t>遅れ</t>
+        <v>2</v>
+      </c>
+      <c r="L4" s="25" t="inlineStr">
+        <is>
+          <t>期限超過（1か月）</t>
         </is>
       </c>
       <c r="M4" s="19" t="inlineStr">
         <is>
-          <t>**令和7年度調査の個票データ（依頼票H16）。地区情報の有無も要確認**</t>
+          <t>**開催日が未定**</t>
         </is>
       </c>
     </row>
@@ -3983,17 +3983,17 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>9-2</t>
+          <t>9-1</t>
         </is>
       </c>
       <c r="C5" s="19" t="inlineStr">
         <is>
-          <t>協議会 第1回（第9期の評価・調査結果）</t>
+          <t>協議会の開催回数・時期の確定</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>町</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="F5" s="20" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="G5" s="25" t="inlineStr">
-        <is>
-          <t>要対応</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H5" s="32" t="n">
@@ -4021,16 +4021,16 @@
         <v>-50</v>
       </c>
       <c r="K5" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" s="25" t="inlineStr">
         <is>
-          <t>期限超過（1か月）</t>
+          <t>期限超過（2か月）</t>
         </is>
       </c>
       <c r="M5" s="19" t="inlineStr">
         <is>
-          <t>**開催日が未定**</t>
+          <t>**町との協議（依頼票C4）。これが決まらないと工程が引けない**</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
     <row r="80">
       <c r="A80" s="34" t="inlineStr">
         <is>
-          <t>加重の実績進捗率 72.0％　対　予定進捗率 63.7％　乖離 +8.2ポイント</t>
+          <t>加重の実績進捗率 72.2％　対　予定進捗率 63.7％　乖離 +8.5ポイント</t>
         </is>
       </c>
     </row>
@@ -12985,20 +12985,20 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K56" s="25" t="inlineStr">
-        <is>
-          <t>要対応</t>
+      <c r="K56" s="23" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="L56" s="22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M56" s="23" t="n">
         <v>1</v>
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>**仕様書に回数の指定がない。**受託者案は4回</t>
+          <t>**10月22日に町から、次回の推進協議会は令和8年12月の開催予定と伺った（回次・議題は確認中）。****仕様書に回数の指定がない。**受託者案は4回</t>
         </is>
       </c>
       <c r="O56" s="19" t="inlineStr">

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261022.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261022.xlsx
@@ -118,12 +118,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4E4"/>
+        <fgColor rgb="00EEEEEE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEEEEE"/>
+        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
     <fill>
@@ -206,7 +206,7 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.7222680412371134</v>
+        <v>0.7403092783505154</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -722,13 +722,13 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.08501030927835046</v>
+        <v>0.1030515463917524</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>おおむね予定どおり 51件／前倒し 17件／遅れ 5件／期限超過（2か月） 2件／期限超過（1か月） 2件</t>
+          <t>おおむね予定どおり 49件／前倒し 19件／遅れ 5件／期限超過（2か月） 2件／期限超過（1か月） 2件</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       <c r="E2" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="27" t="inlineStr">
+      <c r="F2" s="26" t="inlineStr">
         <is>
           <t>前提条項</t>
         </is>
@@ -2215,7 +2215,7 @@
       <c r="E3" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="27" t="inlineStr">
+      <c r="F3" s="26" t="inlineStr">
         <is>
           <t>前提条項</t>
         </is>
@@ -2990,7 +2990,7 @@
       <c r="E27" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F27" s="27" t="inlineStr">
+      <c r="F27" s="26" t="inlineStr">
         <is>
           <t>前提条項</t>
         </is>
@@ -3801,22 +3801,22 @@
     <row r="2">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>P5 第9期の評価</t>
+          <t>P4 調査結果の反映</t>
         </is>
       </c>
       <c r="B2" s="20" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="C2" s="19" t="inlineStr">
         <is>
-          <t>施設整備方針との不整合の確認</t>
+          <t>個票によるクロス集計</t>
         </is>
       </c>
       <c r="D2" s="20" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E2" s="20" t="inlineStr">
@@ -3826,93 +3826,93 @@
       </c>
       <c r="F2" s="20" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G2" s="27" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>データ待ち</t>
         </is>
       </c>
       <c r="H2" s="32" t="n">
         <v>0</v>
       </c>
       <c r="I2" s="32" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="J2" s="32" t="n">
-        <v>-100</v>
+        <v>-85</v>
       </c>
       <c r="K2" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" s="25" t="inlineStr">
-        <is>
-          <t>期限超過（1か月）</t>
+        <v>3</v>
+      </c>
+      <c r="L2" s="27" t="inlineStr">
+        <is>
+          <t>遅れ</t>
         </is>
       </c>
       <c r="M2" s="19" t="inlineStr">
         <is>
-          <t>整備の経緯の確認（依頼票H15）</t>
+          <t>**令和7年度調査の個票データ（依頼票H16）。地区情報の有無も要確認**</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="19" t="inlineStr">
         <is>
-          <t>P4 調査結果の反映</t>
+          <t>P9 意見聴取</t>
         </is>
       </c>
       <c r="B3" s="20" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="C3" s="19" t="inlineStr">
         <is>
-          <t>個票によるクロス集計</t>
+          <t>協議会 第1回（第9期の評価・調査結果）</t>
         </is>
       </c>
       <c r="D3" s="20" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E3" s="20" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="F3" s="20" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="G3" s="26" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
+      <c r="G3" s="25" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="H3" s="32" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I3" s="32" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="J3" s="32" t="n">
-        <v>-85</v>
+        <v>-50</v>
       </c>
       <c r="K3" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="L3" s="26" t="inlineStr">
-        <is>
-          <t>遅れ</t>
+        <v>2</v>
+      </c>
+      <c r="L3" s="25" t="inlineStr">
+        <is>
+          <t>期限超過（1か月）</t>
         </is>
       </c>
       <c r="M3" s="19" t="inlineStr">
         <is>
-          <t>**令和7年度調査の個票データ（依頼票H16）。地区情報の有無も要確認**</t>
+          <t>**開催日が未定**</t>
         </is>
       </c>
     </row>
@@ -3924,17 +3924,17 @@
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>9-2</t>
+          <t>9-1</t>
         </is>
       </c>
       <c r="C4" s="19" t="inlineStr">
         <is>
-          <t>協議会 第1回（第9期の評価・調査結果）</t>
+          <t>協議会の開催回数・時期の確定</t>
         </is>
       </c>
       <c r="D4" s="20" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>町</t>
         </is>
       </c>
       <c r="E4" s="20" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="F4" s="20" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="G4" s="25" t="inlineStr">
-        <is>
-          <t>要対応</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G4" s="23" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H4" s="32" t="n">
@@ -3962,48 +3962,48 @@
         <v>-50</v>
       </c>
       <c r="K4" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L4" s="25" t="inlineStr">
         <is>
-          <t>期限超過（1か月）</t>
+          <t>期限超過（2か月）</t>
         </is>
       </c>
       <c r="M4" s="19" t="inlineStr">
         <is>
-          <t>**開催日が未定**</t>
+          <t>**町との協議（依頼票C4）。これが決まらないと工程が引けない**</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>P9 意見聴取</t>
+          <t>P5 第9期の評価</t>
         </is>
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>9-1</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="C5" s="19" t="inlineStr">
         <is>
-          <t>協議会の開催回数・時期の確定</t>
+          <t>施設整備方針との不整合の確認</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G5" s="23" t="inlineStr">
@@ -4012,47 +4012,47 @@
         </is>
       </c>
       <c r="H5" s="32" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I5" s="32" t="n">
         <v>100</v>
       </c>
       <c r="J5" s="32" t="n">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="K5" s="20" t="n">
         <v>1</v>
       </c>
       <c r="L5" s="25" t="inlineStr">
         <is>
-          <t>期限超過（2か月）</t>
+          <t>期限超過（1か月）</t>
         </is>
       </c>
       <c r="M5" s="19" t="inlineStr">
         <is>
-          <t>**町との協議（依頼票C4）。これが決まらないと工程が引けない**</t>
+          <t>整備の経緯の確認（依頼票H15）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>2-6</t>
+          <t>1-8</t>
         </is>
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>介護予防事業対象者数の分析</t>
+          <t>工程・協議会日程の合意と確認事項の照会</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -4065,58 +4065,58 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="G6" s="26" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
+      <c r="G6" s="25" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="H6" s="32" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="I6" s="32" t="n">
         <v>90.09999999999999</v>
       </c>
       <c r="J6" s="32" t="n">
-        <v>-40.1</v>
+        <v>-35.1</v>
       </c>
       <c r="K6" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="L6" s="26" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L6" s="27" t="inlineStr">
         <is>
           <t>遅れ</t>
         </is>
       </c>
       <c r="M6" s="19" t="inlineStr">
         <is>
-          <t>**町の事業実績（依頼票H3）。見える化の0か所と調査の5.5％が整合しない。****ワークシートに載る実施状況調査の回答も、従前相当の利用者数がほとんど空欄で、実人数と延べ人数が同じ年があり、サービスBの人数が408→24→150→24人と激しく振れている。町の控えとの突合が要る**</t>
+          <t>**町との協議。協議会の回数が決まらないとP6・P8・P9・P10の日程が引けない。最も厳しい案Aでも第1回の期限は11月6日で、残りは1か月である**</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P3 給付費等の分析</t>
         </is>
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>1-8</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t>工程・協議会日程の合意と確認事項の照会</t>
+          <t>町の給付実績との突合</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -4124,53 +4124,53 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
-        <is>
-          <t>要対応</t>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H7" s="32" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="I7" s="32" t="n">
-        <v>90.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="J7" s="32" t="n">
-        <v>-35.1</v>
+        <v>-35</v>
       </c>
       <c r="K7" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" s="26" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="L7" s="27" t="inlineStr">
         <is>
           <t>遅れ</t>
         </is>
       </c>
       <c r="M7" s="19" t="inlineStr">
         <is>
-          <t>**町との協議。協議会の回数が決まらないとP6・P8・P9・P10の日程が引けない。最も厳しい案Aでも第1回の期限は11月6日で、残りは1か月である**</t>
+          <t>見える化システムの値との突合作業</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>P3 給付費等の分析</t>
+          <t>P7 推計・算定</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
-          <t>町の給付実績との突合</t>
+          <t>総合事業費の上限額の確認</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -4180,93 +4180,93 @@
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="G8" s="23" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="G8" s="27" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
         </is>
       </c>
       <c r="H8" s="32" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I8" s="32" t="n">
-        <v>85</v>
+        <v>56.7</v>
       </c>
       <c r="J8" s="32" t="n">
-        <v>-35</v>
+        <v>-31.7</v>
       </c>
       <c r="K8" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="L8" s="26" t="inlineStr">
+      <c r="L8" s="27" t="inlineStr">
         <is>
           <t>遅れ</t>
         </is>
       </c>
       <c r="M8" s="19" t="inlineStr">
         <is>
-          <t>見える化システムの値との突合作業</t>
+          <t>**町の「総合事業上限額算定の手引き（Excel）」（平成27年度〜令和6年度）と地域支援事業交付金事業実績報告書が要る。****現に上限内に収まっているかを確かめられていない。**上限を超えると超過分は町の一般財源となるため、サービスBを広げる場合（決定7）の判断に直結する</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t>P7 推計・算定</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>7-9</t>
+          <t>2-6</t>
         </is>
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t>総合事業費の上限額の確認</t>
+          <t>介護予防事業対象者数の分析</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
         <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="G9" s="26" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H9" s="32" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="I9" s="32" t="n">
-        <v>56.7</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="J9" s="32" t="n">
-        <v>-31.7</v>
+        <v>-20.1</v>
       </c>
       <c r="K9" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="L9" s="26" t="inlineStr">
+      <c r="L9" s="27" t="inlineStr">
         <is>
           <t>遅れ</t>
         </is>
       </c>
       <c r="M9" s="19" t="inlineStr">
         <is>
-          <t>**町の「総合事業上限額算定の手引き（Excel）」（平成27年度〜令和6年度）と地域支援事業交付金事業実績報告書が要る。****現に上限内に収まっているかを確かめられていない。**上限を超えると超過分は町の一般財源となるため、サービスBを広げる場合（決定7）の判断に直結する</t>
+          <t>**町の事業実績（依頼票H3）。見える化の0か所と調査の5.5％が整合しない。****ワークシートに載る実施状況調査の回答も、従前相当の利用者数がほとんど空欄で、実人数と延べ人数が同じ年があり、サービスBの人数が408→24→150→24人と激しく振れている。町の控えとの突合が要る**</t>
         </is>
       </c>
     </row>
@@ -4391,32 +4391,32 @@
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>P3 給付費等の分析</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="C12" s="19" t="inlineStr">
         <is>
-          <t>給付費等分析結果報告書の作成</t>
+          <t>認定者数の異常値の検証</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G12" s="23" t="inlineStr">
@@ -4425,13 +4425,13 @@
         </is>
       </c>
       <c r="H12" s="32" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="I12" s="32" t="n">
-        <v>74.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="J12" s="32" t="n">
-        <v>-4.3</v>
+        <v>-0.1</v>
       </c>
       <c r="K12" s="20" t="n">
         <v>5</v>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="M12" s="19" t="inlineStr">
         <is>
-          <t>町の給付実績（依頼票S1・S2）で数値を確定する</t>
+          <t>**「令和7年8〜9月に計上方法の変更がなかったか」に論点が絞られた。町外施設入所者の帰属、住所地特例、国保連の集計定義のいずれか**</t>
         </is>
       </c>
     </row>
@@ -4455,17 +4455,17 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t>認定者数の異常値の検証</t>
+          <t>認定者数・認定率の分析</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -4475,25 +4475,25 @@
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="G13" s="23" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H13" s="32" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I13" s="32" t="n">
-        <v>90.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="J13" s="32" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L13" s="21" t="inlineStr">
         <is>
@@ -4502,24 +4502,24 @@
       </c>
       <c r="M13" s="19" t="inlineStr">
         <is>
-          <t>**「令和7年8〜9月に計上方法の変更がなかったか」に論点が絞られた。町外施設入所者の帰属、住所地特例、国保連の集計定義のいずれか**</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P4 調査結果の反映</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C14" s="19" t="inlineStr">
         <is>
-          <t>認定者数・認定率の分析</t>
+          <t>集計結果・分析報告書の作成</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -4568,17 +4568,17 @@
     <row r="15">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>P4 調査結果の反映</t>
+          <t>P5 第9期の評価</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
-          <t>集計結果・分析報告書の作成</t>
+          <t>協議会資料（第9期評価・調査結果）の作成</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -4620,24 +4620,24 @@
       </c>
       <c r="M15" s="19" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**開催日が未定。決まればすぐにお出しできる**</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>P5 第9期の評価</t>
+          <t>P7 推計・算定</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>7-1</t>
         </is>
       </c>
       <c r="C16" s="19" t="inlineStr">
         <is>
-          <t>協議会資料（第9期評価・調査結果）の作成</t>
+          <t>算定シートの構築</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -4679,24 +4679,24 @@
       </c>
       <c r="M16" s="19" t="inlineStr">
         <is>
-          <t>**開催日が未定。決まればすぐにお出しできる**</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="19" t="inlineStr">
         <is>
-          <t>P7 推計・算定</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>7-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t>算定シートの構築</t>
+          <t>委託仕様書の確認と適合性チェック</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -4729,7 +4729,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L17" s="21" t="inlineStr">
         <is>
@@ -4750,12 +4750,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="C18" s="19" t="inlineStr">
         <is>
-          <t>委託仕様書の確認と適合性チェック</t>
+          <t>第9期計画本文の確認</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -4804,17 +4804,17 @@
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t>第9期計画本文の確認</t>
+          <t>人口・世帯の分析</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E19" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-12</t>
         </is>
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
-          <t>人口・世帯の分析</t>
+          <t>総合事業の実施状況の分析</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -4883,24 +4883,24 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="G20" s="21" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H20" s="32" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="I20" s="32" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="J20" s="32" t="n">
         <v>0</v>
@@ -4915,24 +4915,24 @@
       </c>
       <c r="M20" s="19" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**ワークシートに載る実施状況調査の回答は、従前相当サービスの利用者数がほとんど空欄で、実人数と延べ人数が同じ年があり、サービスBの人数が408→24→150→24人と激しく振れている。時系列として使えないため、町の控え（平成29年度〜令和6年度）との突合が要る**　**10月1日に通いの場の図を作成（f48）。**見える化は平成28年度以降0か所、調査では13.8％が年に数回以上参加。食い違いの解明は町の事業実績待ち</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P4 調査結果の反映</t>
         </is>
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>2-12</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
-          <t>総合事業の実施状況の分析</t>
+          <t>調査結果報告書の確認</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -4942,24 +4942,24 @@
       </c>
       <c r="E21" s="20" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="G21" s="23" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H21" s="32" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="I21" s="32" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="J21" s="32" t="n">
         <v>0</v>
@@ -4974,24 +4974,24 @@
       </c>
       <c r="M21" s="19" t="inlineStr">
         <is>
-          <t>**ワークシートに載る実施状況調査の回答は、従前相当サービスの利用者数がほとんど空欄で、実人数と延べ人数が同じ年があり、サービスBの人数が408→24→150→24人と激しく振れている。時系列として使えないため、町の控え（平成29年度〜令和6年度）との突合が要る**　**10月1日に通いの場の図を作成（f48）。**見える化は平成28年度以降0か所、調査では13.8％が年に数回以上参加。食い違いの解明は町の事業実績待ち</t>
+          <t>―　**9月29日に調査結果報告書の原本（104頁）を受領し、集計値を1件ずつ突き合わせた（286件・NG0）。**認知症の設問の項目名を原本に合わせ、報告書そのものの食い違い3件を注記した</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>P4 調査結果の反映</t>
+          <t>P7 推計・算定</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>7-5</t>
         </is>
       </c>
       <c r="C22" s="19" t="inlineStr">
         <is>
-          <t>調査結果報告書の確認</t>
+          <t>見える化システムへの入力作業</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -5033,24 +5033,24 @@
       </c>
       <c r="M22" s="19" t="inlineStr">
         <is>
-          <t>―　**9月29日に調査結果報告書の原本（104頁）を受領し、集計値を1件ずつ突き合わせた（286件・NG0）。**認知症の設問の項目名を原本に合わせ、報告書そのものの食い違い3件を注記した</t>
+          <t>**9月24日に、受領したワークシートを1行ずつ読んで入力値を確定した（見える化システム入力値一覧・入力の手順。11_見える化出力依頼）。****入力の前に直す設定が2件ある。**①1人1月あたり給付費の実績値が令和8年度になっている。令和8年度の列は1か月分で、人数・回数・日数の非ゼロ36件のうち31件（86.1％）が整数である（令和6年度は46件中5件、令和7年度は40件中8件で、いずれも12分の1単位の小数）。令和7年度に切り替える。②認定率の伸びが令和6年度→令和7年度になっている。**見える化の認定者数は各年9月末の値で、令和7年度の865人は令和7年9月の断層の直後にあたる。**令和6年度937人は国保連の令和6年10月審査分と一致し、令和7年度865人と令和8年度865人は同値で令和8年度に実績がないことを示す。計上方法の確認が取れるまでこの伸びは使えない。**入力欄は、当方で用意できるものが28欄、町の資料が要るものが26欄。**町の資料が要るのは一般介護予防事業5欄（計5,305千円）、包括的支援事業・任意事業8欄（計29,335千円）、審査支払手数料等2欄（計531千円）、準備基金、令和8年度の当初予算など。**所得段階別加入割合13段階を入れると調整交付金見込交付割合が自動で出るため、当方の算式値（令和9年度6.107％・令和10年度5.548％・令和11年度4.945％）と突き合わせる**</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>P7 推計・算定</t>
+          <t>P8 素案</t>
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>7-5</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="C23" s="19" t="inlineStr">
         <is>
-          <t>見える化システムへの入力作業</t>
+          <t>成果指標の目標値案の作成</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -5092,24 +5092,24 @@
       </c>
       <c r="M23" s="19" t="inlineStr">
         <is>
-          <t>**9月24日に、受領したワークシートを1行ずつ読んで入力値を確定した（見える化システム入力値一覧・入力の手順。11_見える化出力依頼）。****入力の前に直す設定が2件ある。**①1人1月あたり給付費の実績値が令和8年度になっている。令和8年度の列は1か月分で、人数・回数・日数の非ゼロ36件のうち31件（86.1％）が整数である（令和6年度は46件中5件、令和7年度は40件中8件で、いずれも12分の1単位の小数）。令和7年度に切り替える。②認定率の伸びが令和6年度→令和7年度になっている。**見える化の認定者数は各年9月末の値で、令和7年度の865人は令和7年9月の断層の直後にあたる。**令和6年度937人は国保連の令和6年10月審査分と一致し、令和7年度865人と令和8年度865人は同値で令和8年度に実績がないことを示す。計上方法の確認が取れるまでこの伸びは使えない。**入力欄は、当方で用意できるものが28欄、町の資料が要るものが26欄。**町の資料が要るのは一般介護予防事業5欄（計5,305千円）、包括的支援事業・任意事業8欄（計29,335千円）、審査支払手数料等2欄（計531千円）、準備基金、令和8年度の当初予算など。**所得段階別加入割合13段階を入れると調整交付金見込交付割合が自動で出るため、当方の算式値（令和9年度6.107％・令和10年度5.548％・令和11年度4.945％）と突き合わせる**</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>P8 素案</t>
+          <t>P10 完成・納品</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>10-2</t>
         </is>
       </c>
       <c r="C24" s="19" t="inlineStr">
         <is>
-          <t>成果指標の目標値案の作成</t>
+          <t>レイアウト・組版</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -5119,24 +5119,24 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="G24" s="26" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H24" s="32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I24" s="32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J24" s="32" t="n">
         <v>0</v>
@@ -5151,24 +5151,24 @@
       </c>
       <c r="M24" s="19" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>原稿の確定</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>P10 完成・納品</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>10-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>計画書の原稿確定</t>
+          <t>契約・体制の確立、キックオフ</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -5178,30 +5178,30 @@
       </c>
       <c r="E25" s="20" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="G25" s="27" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H25" s="32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I25" s="32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J25" s="32" t="n">
         <v>0</v>
       </c>
       <c r="K25" s="20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L25" s="21" t="inlineStr">
         <is>
@@ -5210,24 +5210,24 @@
       </c>
       <c r="M25" s="19" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>P10 完成・納品</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>10-2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>レイアウト・組版</t>
+          <t>引継ぎ資料の整理</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -5237,30 +5237,30 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="G26" s="27" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H26" s="32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I26" s="32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J26" s="32" t="n">
         <v>0</v>
       </c>
       <c r="K26" s="20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L26" s="21" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="M26" s="19" t="inlineStr">
         <is>
-          <t>原稿の確定</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>契約・体制の確立、キックオフ</t>
+          <t>第3期地域福祉計画との役割分担の整理</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E27" s="20" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1-6</t>
         </is>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>引継ぎ資料の整理</t>
+          <t>町への資料依頼票の作成</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -5394,17 +5394,17 @@
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>1-5</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>第3期地域福祉計画との役割分担の整理</t>
+          <t>サービス受給者数の分析</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="E29" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -5453,17 +5453,17 @@
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>1-6</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>町への資料依頼票の作成</t>
+          <t>サービス自給率の分析</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -5512,17 +5512,17 @@
     <row r="31">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P4 調査結果の反映</t>
         </is>
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>サービス受給者数の分析</t>
+          <t>集計データの整理</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="E31" s="20" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -5571,17 +5571,17 @@
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P4 調査結果の反映</t>
         </is>
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>4-4</t>
         </is>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>サービス自給率の分析</t>
+          <t>クロス集計の設計</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -5630,44 +5630,44 @@
     <row r="33">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>P4 調査結果の反映</t>
+          <t>P6 骨子案</t>
         </is>
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>6-2</t>
         </is>
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t>集計データの整理</t>
+          <t>骨子案の協議（協議会）</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="G33" s="21" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="G33" s="26" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H33" s="32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I33" s="32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J33" s="32" t="n">
         <v>0</v>
@@ -5682,24 +5682,24 @@
       </c>
       <c r="M33" s="19" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**協議会の開催回数・時期が未定（依頼票C4）**</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
         <is>
-          <t>P4 調査結果の反映</t>
+          <t>P7 推計・算定</t>
         </is>
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>4-4</t>
+          <t>7-2</t>
         </is>
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>クロス集計の設計</t>
+          <t>保険料算定のケース設定の確定</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -5748,44 +5748,44 @@
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>P6 骨子案</t>
+          <t>P8 素案</t>
         </is>
       </c>
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>6-2</t>
+          <t>8-3</t>
         </is>
       </c>
       <c r="C35" s="19" t="inlineStr">
         <is>
-          <t>骨子案の協議（協議会）</t>
+          <t>認知症施策推進基本計画の包含方針</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
         <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="G35" s="27" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G35" s="21" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H35" s="32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I35" s="32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J35" s="32" t="n">
         <v>0</v>
@@ -5800,51 +5800,51 @@
       </c>
       <c r="M35" s="19" t="inlineStr">
         <is>
-          <t>**協議会の開催回数・時期が未定（依頼票C4）**</t>
+          <t>**認知症の人及びその家族等の意見をどう聴くか（同法13条3項→12条3項）。記述の追加では埋まらず策定過程に関わるため、協議会の委員構成を確認したうえで家族会・認知症カフェでの意見聴取の機会を設けるかを町と協議する。**あわせて福島県の認知症施策推進計画の策定状況、町の意思決定（方式A／B）</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>P7 推計・算定</t>
+          <t>P8 素案</t>
         </is>
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>7-2</t>
+          <t>8-5</t>
         </is>
       </c>
       <c r="C36" s="19" t="inlineStr">
         <is>
-          <t>保険料算定のケース設定の確定</t>
+          <t>素案の協議（協議会）</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="G36" s="21" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="G36" s="26" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H36" s="32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I36" s="32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J36" s="32" t="n">
         <v>0</v>
@@ -5859,51 +5859,51 @@
       </c>
       <c r="M36" s="19" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>協議会の開催時期</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>P8 素案</t>
+          <t>P9 意見聴取</t>
         </is>
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>8-3</t>
+          <t>9-4</t>
         </is>
       </c>
       <c r="C37" s="19" t="inlineStr">
         <is>
-          <t>認知症施策推進基本計画の包含方針</t>
+          <t>協議会 第3回（素案）</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="G37" s="21" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="G37" s="26" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H37" s="32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I37" s="32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J37" s="32" t="n">
         <v>0</v>
@@ -5918,51 +5918,51 @@
       </c>
       <c r="M37" s="19" t="inlineStr">
         <is>
-          <t>**認知症の人及びその家族等の意見をどう聴くか（同法13条3項→12条3項）。記述の追加では埋まらず策定過程に関わるため、協議会の委員構成を確認したうえで家族会・認知症カフェでの意見聴取の機会を設けるかを町と協議する。**あわせて福島県の認知症施策推進計画の策定状況、町の意思決定（方式A／B）</t>
+          <t>素案の確定</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>P8 素案</t>
+          <t>P9 意見聴取</t>
         </is>
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>8-5</t>
+          <t>9-5</t>
         </is>
       </c>
       <c r="C38" s="19" t="inlineStr">
         <is>
-          <t>素案の協議（協議会）</t>
+          <t>パブリックコメントの様式作成</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="G38" s="27" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G38" s="21" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H38" s="32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I38" s="32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J38" s="32" t="n">
         <v>0</v>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="M38" s="19" t="inlineStr">
         <is>
-          <t>協議会の開催時期</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -5989,30 +5989,30 @@
       </c>
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>9-4</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="C39" s="19" t="inlineStr">
         <is>
-          <t>協議会 第3回（素案）</t>
+          <t>パブリックコメントの実施</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>町</t>
         </is>
       </c>
       <c r="E39" s="20" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="F39" s="20" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="G39" s="27" t="inlineStr">
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="G39" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="M39" s="19" t="inlineStr">
         <is>
-          <t>素案の確定</t>
+          <t>素案の確定、実施時期の確定（依頼票C6）</t>
         </is>
       </c>
     </row>
@@ -6048,12 +6048,12 @@
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="C40" s="19" t="inlineStr">
         <is>
-          <t>パブリックコメントの様式作成</t>
+          <t>意見への対応</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
@@ -6063,24 +6063,24 @@
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="G40" s="21" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="G40" s="26" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H40" s="32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I40" s="32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J40" s="32" t="n">
         <v>0</v>
@@ -6095,42 +6095,42 @@
       </c>
       <c r="M40" s="19" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>パブコメの実施</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="19" t="inlineStr">
         <is>
-          <t>P9 意見聴取</t>
+          <t>P10 完成・納品</t>
         </is>
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>10-3</t>
         </is>
       </c>
       <c r="C41" s="19" t="inlineStr">
         <is>
-          <t>パブリックコメントの実施</t>
+          <t>校正（初校・再校・校了）</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E41" s="20" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
         <is>
-          <t>2027-01</t>
-        </is>
-      </c>
-      <c r="G41" s="27" t="inlineStr">
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="G41" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -6154,24 +6154,24 @@
       </c>
       <c r="M41" s="19" t="inlineStr">
         <is>
-          <t>素案の確定、実施時期の確定（依頼票C6）</t>
+          <t>組版</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>P9 意見聴取</t>
+          <t>P10 完成・納品</t>
         </is>
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>10-5</t>
         </is>
       </c>
       <c r="C42" s="19" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>概要版の作成</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
@@ -6186,10 +6186,10 @@
       </c>
       <c r="F42" s="20" t="inlineStr">
         <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="G42" s="27" t="inlineStr">
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="G42" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -6213,7 +6213,7 @@
       </c>
       <c r="M42" s="19" t="inlineStr">
         <is>
-          <t>パブコメの実施</t>
+          <t>計画書の確定</t>
         </is>
       </c>
     </row>
@@ -6225,30 +6225,30 @@
       </c>
       <c r="B43" s="20" t="inlineStr">
         <is>
-          <t>10-3</t>
+          <t>10-6</t>
         </is>
       </c>
       <c r="C43" s="19" t="inlineStr">
         <is>
-          <t>校正（初校・再校・校了）</t>
+          <t>印刷・製本</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E43" s="20" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="F43" s="20" t="inlineStr">
         <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="G43" s="27" t="inlineStr">
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="G43" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -6272,24 +6272,24 @@
       </c>
       <c r="M43" s="19" t="inlineStr">
         <is>
-          <t>組版</t>
+          <t>校了</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="19" t="inlineStr">
         <is>
-          <t>P10 完成・納品</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>10-5</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C44" s="19" t="inlineStr">
         <is>
-          <t>概要版の作成</t>
+          <t>第1号被保険者の分析</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
@@ -6299,30 +6299,30 @@
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F44" s="20" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="G44" s="27" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G44" s="21" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H44" s="32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I44" s="32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J44" s="32" t="n">
         <v>0</v>
       </c>
       <c r="K44" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L44" s="21" t="inlineStr">
         <is>
@@ -6331,24 +6331,24 @@
       </c>
       <c r="M44" s="19" t="inlineStr">
         <is>
-          <t>計画書の確定</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="19" t="inlineStr">
         <is>
-          <t>P10 完成・納品</t>
+          <t>P3 給付費等の分析</t>
         </is>
       </c>
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>10-6</t>
+          <t>3-3</t>
         </is>
       </c>
       <c r="C45" s="19" t="inlineStr">
         <is>
-          <t>印刷・製本</t>
+          <t>成果品①の製本・納品</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
@@ -6366,7 +6366,7 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="G45" s="27" t="inlineStr">
+      <c r="G45" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="K45" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L45" s="21" t="inlineStr">
         <is>
@@ -6390,24 +6390,24 @@
       </c>
       <c r="M45" s="19" t="inlineStr">
         <is>
-          <t>校了</t>
+          <t>報告書の確定</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="19" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P4 調査結果の反映</t>
         </is>
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C46" s="19" t="inlineStr">
         <is>
-          <t>第1号被保険者の分析</t>
+          <t>レッドチームレビュー</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E46" s="20" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F46" s="20" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G46" s="21" t="inlineStr">
@@ -6456,17 +6456,17 @@
     <row r="47">
       <c r="A47" s="19" t="inlineStr">
         <is>
-          <t>P3 給付費等の分析</t>
+          <t>P6 骨子案</t>
         </is>
       </c>
       <c r="B47" s="20" t="inlineStr">
         <is>
-          <t>3-3</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="C47" s="19" t="inlineStr">
         <is>
-          <t>成果品①の製本・納品</t>
+          <t>成果品③の製本・納品</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
@@ -6484,7 +6484,7 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="G47" s="27" t="inlineStr">
+      <c r="G47" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -6508,24 +6508,24 @@
       </c>
       <c r="M47" s="19" t="inlineStr">
         <is>
-          <t>報告書の確定</t>
+          <t>骨子案の確定</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="19" t="inlineStr">
         <is>
-          <t>P4 調査結果の反映</t>
+          <t>P7 推計・算定</t>
         </is>
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>7-8</t>
         </is>
       </c>
       <c r="C48" s="19" t="inlineStr">
         <is>
-          <t>レッドチームレビュー</t>
+          <t>成果品②の製本・納品</t>
         </is>
       </c>
       <c r="D48" s="20" t="inlineStr">
@@ -6535,24 +6535,24 @@
       </c>
       <c r="E48" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="F48" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="G48" s="21" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="G48" s="26" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H48" s="32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I48" s="32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J48" s="32" t="n">
         <v>0</v>
@@ -6567,24 +6567,24 @@
       </c>
       <c r="M48" s="19" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>報告書の確定</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="19" t="inlineStr">
         <is>
-          <t>P6 骨子案</t>
+          <t>P8 素案</t>
         </is>
       </c>
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>8-6</t>
         </is>
       </c>
       <c r="C49" s="19" t="inlineStr">
         <is>
-          <t>成果品③の製本・納品</t>
+          <t>成果品④の製本・納品</t>
         </is>
       </c>
       <c r="D49" s="20" t="inlineStr">
@@ -6602,7 +6602,7 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="G49" s="27" t="inlineStr">
+      <c r="G49" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -6626,42 +6626,42 @@
       </c>
       <c r="M49" s="19" t="inlineStr">
         <is>
-          <t>骨子案の確定</t>
+          <t>素案の確定</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="19" t="inlineStr">
         <is>
-          <t>P7 推計・算定</t>
+          <t>P9 意見聴取</t>
         </is>
       </c>
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>9-8</t>
         </is>
       </c>
       <c r="C50" s="19" t="inlineStr">
         <is>
-          <t>成果品②の製本・納品</t>
+          <t>協議会 第4回（最終案）</t>
         </is>
       </c>
       <c r="D50" s="20" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="F50" s="20" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="G50" s="27" t="inlineStr">
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="G50" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -6685,24 +6685,24 @@
       </c>
       <c r="M50" s="19" t="inlineStr">
         <is>
-          <t>報告書の確定</t>
+          <t>意見への対応</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="19" t="inlineStr">
         <is>
-          <t>P8 素案</t>
+          <t>P10 完成・納品</t>
         </is>
       </c>
       <c r="B51" s="20" t="inlineStr">
         <is>
-          <t>8-6</t>
+          <t>10-7</t>
         </is>
       </c>
       <c r="C51" s="19" t="inlineStr">
         <is>
-          <t>成果品④の製本・納品</t>
+          <t>データCD-Rの作成</t>
         </is>
       </c>
       <c r="D51" s="20" t="inlineStr">
@@ -6720,7 +6720,7 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="G51" s="27" t="inlineStr">
+      <c r="G51" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -6744,24 +6744,24 @@
       </c>
       <c r="M51" s="19" t="inlineStr">
         <is>
-          <t>素案の確定</t>
+          <t>各成果品の確定</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="19" t="inlineStr">
         <is>
-          <t>P9 意見聴取</t>
+          <t>P10 完成・納品</t>
         </is>
       </c>
       <c r="B52" s="20" t="inlineStr">
         <is>
-          <t>9-8</t>
+          <t>10-8</t>
         </is>
       </c>
       <c r="C52" s="19" t="inlineStr">
         <is>
-          <t>協議会 第4回（最終案）</t>
+          <t>納品・検収</t>
         </is>
       </c>
       <c r="D52" s="20" t="inlineStr">
@@ -6771,15 +6771,15 @@
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="F52" s="20" t="inlineStr">
         <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="G52" s="27" t="inlineStr">
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="G52" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -6803,57 +6803,57 @@
       </c>
       <c r="M52" s="19" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>全成果品の完成</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="19" t="inlineStr">
         <is>
-          <t>P10 完成・納品</t>
+          <t>P8 素案</t>
         </is>
       </c>
       <c r="B53" s="20" t="inlineStr">
         <is>
-          <t>10-7</t>
+          <t>8-8</t>
         </is>
       </c>
       <c r="C53" s="19" t="inlineStr">
         <is>
-          <t>データCD-Rの作成</t>
+          <t>在宅医療・介護連携の目指すべき姿の設定</t>
         </is>
       </c>
       <c r="D53" s="20" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E53" s="20" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F53" s="20" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="G53" s="27" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="G53" s="23" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H53" s="32" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I53" s="32" t="n">
-        <v>0</v>
+        <v>42.1</v>
       </c>
       <c r="J53" s="32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="K53" s="20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L53" s="21" t="inlineStr">
         <is>
@@ -6862,57 +6862,57 @@
       </c>
       <c r="M53" s="19" t="inlineStr">
         <is>
-          <t>各成果品の確定</t>
+          <t>**目指すべき姿の内容の確定（決定11）。公立小野町地方綜合病院・田村郡医師会等との調整が要る。**あわせて在宅医療・介護連携推進事業の実施状況（相談窓口の運営、多職種研修、情報共有ツール）</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="19" t="inlineStr">
         <is>
-          <t>P10 完成・納品</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="B54" s="20" t="inlineStr">
         <is>
-          <t>10-8</t>
+          <t>2-9</t>
         </is>
       </c>
       <c r="C54" s="19" t="inlineStr">
         <is>
-          <t>納品・検収</t>
+          <t>介護保険財政の分析</t>
         </is>
       </c>
       <c r="D54" s="20" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F54" s="20" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="G54" s="27" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G54" s="23" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H54" s="32" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I54" s="32" t="n">
-        <v>0</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="J54" s="32" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="K54" s="20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L54" s="21" t="inlineStr">
         <is>
@@ -6921,29 +6921,29 @@
       </c>
       <c r="M54" s="19" t="inlineStr">
         <is>
-          <t>全成果品の完成</t>
+          <t>**令和7年度の様式4が全て0で未入力。年報 様式4の基金保有額（令和5・6年度末12百万円）は財務書類と合わない。基金は令和8年度末見込210.0百万円。令和7年度末の残高（財産に関する調書）の確認が要る**</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="19" t="inlineStr">
         <is>
-          <t>P8 素案</t>
+          <t>P7 推計・算定</t>
         </is>
       </c>
       <c r="B55" s="20" t="inlineStr">
         <is>
-          <t>8-8</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="C55" s="19" t="inlineStr">
         <is>
-          <t>在宅医療・介護連携の目指すべき姿の設定</t>
+          <t>被保険者数・認定者数の推計</t>
         </is>
       </c>
       <c r="D55" s="20" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E55" s="20" t="inlineStr">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="F55" s="20" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G55" s="23" t="inlineStr">
@@ -6962,16 +6962,16 @@
         </is>
       </c>
       <c r="H55" s="32" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="I55" s="32" t="n">
-        <v>42.1</v>
+        <v>85</v>
       </c>
       <c r="J55" s="32" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="K55" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L55" s="21" t="inlineStr">
         <is>
@@ -6980,24 +6980,24 @@
       </c>
       <c r="M55" s="19" t="inlineStr">
         <is>
-          <t>**目指すべき姿の内容の確定（決定11）。公立小野町地方綜合病院・田村郡医師会等との調整が要る。**あわせて在宅医療・介護連携推進事業の実施状況（相談窓口の運営、多職種研修、情報共有ツール）</t>
+          <t>**認定率をどの水準で置くか（令和7年度実績か、計上変更前の令和6年度水準か）。2-4の確認結果しだいで前提が変わる。**あわせて、認定率の分子に第2号被保険者の認定者を含むかを見える化の画面で確認する（確認事項No.125）</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="19" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P5 第9期の評価</t>
         </is>
       </c>
       <c r="B56" s="20" t="inlineStr">
         <is>
-          <t>2-9</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="C56" s="19" t="inlineStr">
         <is>
-          <t>介護保険財政の分析</t>
+          <t>成果目標の達成状況の確定</t>
         </is>
       </c>
       <c r="D56" s="20" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F56" s="20" t="inlineStr">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="H56" s="32" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="I56" s="32" t="n">
-        <v>90.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="J56" s="32" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K56" s="20" t="n">
         <v>3</v>
@@ -7039,24 +7039,24 @@
       </c>
       <c r="M56" s="19" t="inlineStr">
         <is>
-          <t>**令和7年度の様式4が全て0で未入力。年報 様式4の基金保有額（令和5・6年度末12百万円）は財務書類と合わない。基金は令和8年度末見込210.0百万円。令和7年度末の残高（財産に関する調書）の確認が要る**</t>
+          <t>**地域支援事業費の実績（年報 様式4の令和6・7年度が未入力。依頼票H3）と成果指標の現状値（H1〜H15）。令和8年度は年度途中のため令和9年夏の年報を待つ**</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="19" t="inlineStr">
         <is>
-          <t>P7 推計・算定</t>
+          <t>P10 完成・納品</t>
         </is>
       </c>
       <c r="B57" s="20" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>10-1</t>
         </is>
       </c>
       <c r="C57" s="19" t="inlineStr">
         <is>
-          <t>被保険者数・認定者数の推計</t>
+          <t>計画書の原稿確定</t>
         </is>
       </c>
       <c r="D57" s="20" t="inlineStr">
@@ -7066,30 +7066,30 @@
       </c>
       <c r="E57" s="20" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="F57" s="20" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="G57" s="23" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="G57" s="26" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H57" s="32" t="n">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="I57" s="32" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="J57" s="32" t="n">
         <v>5</v>
       </c>
       <c r="K57" s="20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L57" s="21" t="inlineStr">
         <is>
@@ -7098,24 +7098,24 @@
       </c>
       <c r="M57" s="19" t="inlineStr">
         <is>
-          <t>**認定率をどの水準で置くか（令和7年度実績か、計上変更前の令和6年度水準か）。2-4の確認結果しだいで前提が変わる。**あわせて、認定率の分子に第2号被保険者の認定者を含むかを見える化の画面で確認する（確認事項No.125）</t>
+          <t>意見への対応</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="19" t="inlineStr">
         <is>
-          <t>P5 第9期の評価</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="B58" s="20" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>2-13</t>
         </is>
       </c>
       <c r="C58" s="19" t="inlineStr">
         <is>
-          <t>成果目標の達成状況の確定</t>
+          <t>地域分析・検討シートの記入案の作成</t>
         </is>
       </c>
       <c r="D58" s="20" t="inlineStr">
@@ -7148,7 +7148,7 @@
         <v>5</v>
       </c>
       <c r="K58" s="20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L58" s="21" t="inlineStr">
         <is>
@@ -7157,24 +7157,24 @@
       </c>
       <c r="M58" s="19" t="inlineStr">
         <is>
-          <t>**地域支援事業費の実績（年報 様式4の令和6・7年度が未入力。依頼票H3）と成果指標の現状値（H1〜H15）。令和8年度は年度途中のため令和9年夏の年報を待つ**</t>
+          <t>**町の確定稿への記入は町が行う。記入案のうち通いの場・総合事業に関する記述は2-6・2-12と同じデータ待ちで、町の事業実績が入ると書き換えが要る**</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="19" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P10 完成・納品</t>
         </is>
       </c>
       <c r="B59" s="20" t="inlineStr">
         <is>
-          <t>2-13</t>
+          <t>10-4</t>
         </is>
       </c>
       <c r="C59" s="19" t="inlineStr">
         <is>
-          <t>地域分析・検討シートの記入案の作成</t>
+          <t>概要版の構成案</t>
         </is>
       </c>
       <c r="D59" s="20" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="E59" s="20" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F59" s="20" t="inlineStr">
@@ -7192,22 +7192,22 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="G59" s="23" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="G59" s="21" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H59" s="32" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I59" s="32" t="n">
-        <v>85</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="J59" s="32" t="n">
-        <v>5</v>
+        <v>9.9</v>
       </c>
       <c r="K59" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L59" s="21" t="inlineStr">
         <is>
@@ -7216,24 +7216,24 @@
       </c>
       <c r="M59" s="19" t="inlineStr">
         <is>
-          <t>**町の確定稿への記入は町が行う。記入案のうち通いの場・総合事業に関する記述は2-6・2-12と同じデータ待ちで、町の事業実績が入ると書き換えが要る**</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="19" t="inlineStr">
         <is>
-          <t>P6 骨子案</t>
+          <t>P3 給付費等の分析</t>
         </is>
       </c>
       <c r="B60" s="20" t="inlineStr">
         <is>
-          <t>6-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C60" s="19" t="inlineStr">
         <is>
-          <t>骨子案の作成</t>
+          <t>給付費等分析結果報告書の作成</t>
         </is>
       </c>
       <c r="D60" s="20" t="inlineStr">
@@ -7257,42 +7257,42 @@
         </is>
       </c>
       <c r="H60" s="32" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I60" s="32" t="n">
         <v>74.3</v>
       </c>
       <c r="J60" s="32" t="n">
-        <v>5.7</v>
+        <v>10.7</v>
       </c>
       <c r="K60" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L60" s="21" t="inlineStr">
-        <is>
-          <t>おおむね予定どおり</t>
+        <v>5</v>
+      </c>
+      <c r="L60" s="33" t="inlineStr">
+        <is>
+          <t>前倒し</t>
         </is>
       </c>
       <c r="M60" s="19" t="inlineStr">
         <is>
-          <t>実績データによる数値の確定</t>
+          <t>町の給付実績（依頼票S1・S2）で数値を確定する</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="19" t="inlineStr">
         <is>
-          <t>P10 完成・納品</t>
+          <t>P11 品質・進捗管理</t>
         </is>
       </c>
       <c r="B61" s="20" t="inlineStr">
         <is>
-          <t>10-4</t>
+          <t>11-5</t>
         </is>
       </c>
       <c r="C61" s="19" t="inlineStr">
         <is>
-          <t>概要版の構成案</t>
+          <t>他団体の資料・データの取扱いの点検</t>
         </is>
       </c>
       <c r="D61" s="20" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="E61" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F61" s="20" t="inlineStr">
@@ -7319,17 +7319,17 @@
         <v>100</v>
       </c>
       <c r="I61" s="32" t="n">
-        <v>90.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="J61" s="32" t="n">
-        <v>9.9</v>
+        <v>15</v>
       </c>
       <c r="K61" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L61" s="21" t="inlineStr">
-        <is>
-          <t>おおむね予定どおり</t>
+        <v>2</v>
+      </c>
+      <c r="L61" s="33" t="inlineStr">
+        <is>
+          <t>前倒し</t>
         </is>
       </c>
       <c r="M61" s="19" t="inlineStr">
@@ -7341,22 +7341,22 @@
     <row r="62">
       <c r="A62" s="19" t="inlineStr">
         <is>
-          <t>P11 品質・進捗管理</t>
+          <t>P8 素案</t>
         </is>
       </c>
       <c r="B62" s="20" t="inlineStr">
         <is>
-          <t>11-5</t>
+          <t>8-7</t>
         </is>
       </c>
       <c r="C62" s="19" t="inlineStr">
         <is>
-          <t>他団体の資料・データの取扱いの点検</t>
+          <t>介護給付適正化計画の位置づけと主要3事業の定量目標</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E62" s="20" t="inlineStr">
@@ -7366,25 +7366,25 @@
       </c>
       <c r="F62" s="20" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="G62" s="21" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="G62" s="23" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H62" s="32" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="I62" s="32" t="n">
-        <v>85</v>
+        <v>42.1</v>
       </c>
       <c r="J62" s="32" t="n">
-        <v>15</v>
+        <v>17.9</v>
       </c>
       <c r="K62" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L62" s="33" t="inlineStr">
         <is>
@@ -7393,29 +7393,29 @@
       </c>
       <c r="M62" s="19" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**位置づけの決定（決定9）と、ケアプラン点検の点検件数の目標（決定10）。****あわせて、令和6年度のケアプラン点検の実施件数（0点の理由が件数の少なさか報告していないことかの特定）と、要介護認定の適正化の実施内容（認定調査の委託の有無と点検件数）が要る**</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="19" t="inlineStr">
         <is>
-          <t>P8 素案</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="B63" s="20" t="inlineStr">
         <is>
-          <t>8-7</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C63" s="19" t="inlineStr">
         <is>
-          <t>介護給付適正化計画の位置づけと主要3事業の定量目標</t>
+          <t>見える化 優先度C分野の出力</t>
         </is>
       </c>
       <c r="D63" s="20" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E63" s="20" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="F63" s="20" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="G63" s="23" t="inlineStr">
@@ -7434,16 +7434,16 @@
         </is>
       </c>
       <c r="H63" s="32" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="I63" s="32" t="n">
-        <v>42.1</v>
+        <v>56.7</v>
       </c>
       <c r="J63" s="32" t="n">
-        <v>17.9</v>
+        <v>18.3</v>
       </c>
       <c r="K63" s="20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L63" s="33" t="inlineStr">
         <is>
@@ -7452,24 +7452,24 @@
       </c>
       <c r="M63" s="19" t="inlineStr">
         <is>
-          <t>**位置づけの決定（決定9）と、ケアプラン点検の点検件数の目標（決定10）。****あわせて、令和6年度のケアプラン点検の実施件数（0点の理由が件数の少なさか報告していないことかの特定）と、要介護認定の適正化の実施内容（認定調査の委託の有無と点検件数）が要る**</t>
+          <t>**残るのは医療提供体制・リハビリ提供体制の出力。見える化システムへのアクセスは確保できている（9月28日に推計が通った）**</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="19" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P6 骨子案</t>
         </is>
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>6-1</t>
         </is>
       </c>
       <c r="C64" s="19" t="inlineStr">
         <is>
-          <t>見える化 優先度C分野の出力</t>
+          <t>骨子案の作成</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="E64" s="20" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F64" s="20" t="inlineStr">
@@ -7493,16 +7493,16 @@
         </is>
       </c>
       <c r="H64" s="32" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="I64" s="32" t="n">
-        <v>56.7</v>
+        <v>74.3</v>
       </c>
       <c r="J64" s="32" t="n">
-        <v>18.3</v>
+        <v>20.7</v>
       </c>
       <c r="K64" s="20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L64" s="33" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="M64" s="19" t="inlineStr">
         <is>
-          <t>**残るのは医療提供体制・リハビリ提供体制の出力。見える化システムへのアクセスは確保できている（9月28日に推計が通った）**</t>
+          <t>実績データによる数値の確定</t>
         </is>
       </c>
     </row>
@@ -7695,32 +7695,32 @@
     <row r="68">
       <c r="A68" s="19" t="inlineStr">
         <is>
-          <t>P9 意見聴取</t>
+          <t>P11 品質・進捗管理</t>
         </is>
       </c>
       <c r="B68" s="20" t="inlineStr">
         <is>
-          <t>9-3</t>
+          <t>11-4</t>
         </is>
       </c>
       <c r="C68" s="19" t="inlineStr">
         <is>
-          <t>協議会 第2回（骨子案・見込量・保険料・成果指標）</t>
+          <t>成果品の体裁の統一と機械点検</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F68" s="20" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G68" s="23" t="inlineStr">
@@ -7729,13 +7729,13 @@
         </is>
       </c>
       <c r="H68" s="32" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="I68" s="32" t="n">
-        <v>0</v>
+        <v>42.1</v>
       </c>
       <c r="J68" s="32" t="n">
-        <v>40</v>
+        <v>42.9</v>
       </c>
       <c r="K68" s="20" t="n">
         <v>2</v>
@@ -7747,24 +7747,24 @@
       </c>
       <c r="M68" s="19" t="inlineStr">
         <is>
-          <t>開催日の確定（案Aなら11月27日が期限）</t>
+          <t>**印刷用の最終体裁（4色刷り・80頁）は組版工程（10-2）で別に点検する**</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="19" t="inlineStr">
         <is>
-          <t>P11 品質・進捗管理</t>
+          <t>P7 推計・算定</t>
         </is>
       </c>
       <c r="B69" s="20" t="inlineStr">
         <is>
-          <t>11-4</t>
+          <t>7-4</t>
         </is>
       </c>
       <c r="C69" s="19" t="inlineStr">
         <is>
-          <t>成果品の体裁の統一と機械点検</t>
+          <t>サービス見込量の推計</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
@@ -7779,25 +7779,25 @@
       </c>
       <c r="F69" s="20" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="G69" s="23" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="G69" s="21" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H69" s="32" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="I69" s="32" t="n">
-        <v>42.1</v>
+        <v>56.7</v>
       </c>
       <c r="J69" s="32" t="n">
-        <v>42.9</v>
+        <v>43.3</v>
       </c>
       <c r="K69" s="20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L69" s="33" t="inlineStr">
         <is>
@@ -7806,24 +7806,24 @@
       </c>
       <c r="M69" s="19" t="inlineStr">
         <is>
-          <t>**印刷用の最終体裁（4色刷り・80頁）は組版工程（10-2）で別に点検する**</t>
+          <t>**基準期間の切替を月報の前年同期比で判定する形に改めた。**①令和7年度の件数が3年平均から5％以上離れ、②令和8年度の前年同期比がその向きを裏づけるサービスだけ令和7年度単年にする。訪問看護・介護予防通所リハビリテーション・介護予防福祉用具貸与・介護予防支援・認知症対応型共同生活介護（介護・予防）の6件が該当。判定は check_base() が月報から再計算し、07_基準期間の判定 に載せている</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="19" t="inlineStr">
         <is>
-          <t>P7 推計・算定</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="B70" s="20" t="inlineStr">
         <is>
-          <t>7-4</t>
+          <t>2-11</t>
         </is>
       </c>
       <c r="C70" s="19" t="inlineStr">
         <is>
-          <t>サービス見込量の推計</t>
+          <t>保険者機能強化推進交付金等の評価結果の整理</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
@@ -7856,7 +7856,7 @@
         <v>43.3</v>
       </c>
       <c r="K70" s="20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L70" s="33" t="inlineStr">
         <is>
@@ -7865,24 +7865,24 @@
       </c>
       <c r="M70" s="19" t="inlineStr">
         <is>
-          <t>**基準期間の切替を月報の前年同期比で判定する形に改めた。**①令和7年度の件数が3年平均から5％以上離れ、②令和8年度の前年同期比がその向きを裏づけるサービスだけ令和7年度単年にする。訪問看護・介護予防通所リハビリテーション・介護予防福祉用具貸与・介護予防支援・認知症対応型共同生活介護（介護・予防）の6件が該当。判定は check_base() が月報から再計算し、07_基準期間の判定 に載せている</t>
+          <t>**①令和6年度のケアプラン点検の実施件数（0点の理由の特定）②令和8年度の該当状況調査票の控え（体制・取組で得点した項目の根拠資料）③介護給付費適正化方策とその評価指標を定めた文書（指標1イ・8点の根拠）④広域連合分の集計表（公表順位の母数での位置）**</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="19" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P8 素案</t>
         </is>
       </c>
       <c r="B71" s="20" t="inlineStr">
         <is>
-          <t>2-11</t>
+          <t>8-1</t>
         </is>
       </c>
       <c r="C71" s="19" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果の整理</t>
+          <t>素案の作成</t>
         </is>
       </c>
       <c r="D71" s="20" t="inlineStr">
@@ -7892,30 +7892,30 @@
       </c>
       <c r="E71" s="20" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F71" s="20" t="inlineStr">
         <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="G71" s="21" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="G71" s="23" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H71" s="32" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I71" s="32" t="n">
-        <v>56.7</v>
+        <v>53.9</v>
       </c>
       <c r="J71" s="32" t="n">
-        <v>43.3</v>
+        <v>44.1</v>
       </c>
       <c r="K71" s="20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L71" s="33" t="inlineStr">
         <is>
@@ -7924,24 +7924,24 @@
       </c>
       <c r="M71" s="19" t="inlineStr">
         <is>
-          <t>**①令和6年度のケアプラン点検の実施件数（0点の理由の特定）②令和8年度の該当状況調査票の控え（体制・取組で得点した項目の根拠資料）③介護給付費適正化方策とその評価指標を定めた文書（指標1イ・8点の根拠）④広域連合分の集計表（公表順位の母数での位置）**</t>
+          <t>**9月24日に、受託者が算定すべき未確定箇所をすべて解消した。**所得段階別保険料率を13段階すべてについて算定し（乗率・年額・被保険者数・構成比）、必要利用定員総数・地域支援事業の量・認知症高齢者数を加えた。**未確定は158箇所→94箇所となり、【算定後に記載】は0件になった。****あわせて数値2件を原本で確かめた。**①所得第2段階の乗率は0.485とした。第9期計画本文が「基準額×0.485」「年額38,500円」と明記しており、79,200円×0.485＝38,412円の100円未満切上げで38,500円になる。年報の令和7年度は486となっているが、令和6年度は485である。②所得第1〜3段階の割合は、1,094人÷3,443人で31.8％である。**第2章1の人口（見える化の将来推計・暦年）と第2章6の被保険者数（第10期将来推計用推計人口・年度）が別系列であることを注記した。**従前の注は「保険料算定との整合のため見える化の推計を用いる」と書いていたが、保険料算定は後者を用いており誤りであった</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="19" t="inlineStr">
         <is>
-          <t>P8 素案</t>
+          <t>P11 品質・進捗管理</t>
         </is>
       </c>
       <c r="B72" s="20" t="inlineStr">
         <is>
-          <t>8-1</t>
+          <t>11-2</t>
         </is>
       </c>
       <c r="C72" s="19" t="inlineStr">
         <is>
-          <t>素案の作成</t>
+          <t>図表データ管理台帳の整備と運用</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F72" s="20" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G72" s="23" t="inlineStr">
@@ -7965,16 +7965,16 @@
         </is>
       </c>
       <c r="H72" s="32" t="n">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="I72" s="32" t="n">
-        <v>53.9</v>
+        <v>28.3</v>
       </c>
       <c r="J72" s="32" t="n">
-        <v>44.1</v>
+        <v>56.7</v>
       </c>
       <c r="K72" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L72" s="33" t="inlineStr">
         <is>
@@ -7983,39 +7983,39 @@
       </c>
       <c r="M72" s="19" t="inlineStr">
         <is>
-          <t>**9月24日に、受託者が算定すべき未確定箇所をすべて解消した。**所得段階別保険料率を13段階すべてについて算定し（乗率・年額・被保険者数・構成比）、必要利用定員総数・地域支援事業の量・認知症高齢者数を加えた。**未確定は158箇所→94箇所となり、【算定後に記載】は0件になった。****あわせて数値2件を原本で確かめた。**①所得第2段階の乗率は0.485とした。第9期計画本文が「基準額×0.485」「年額38,500円」と明記しており、79,200円×0.485＝38,412円の100円未満切上げで38,500円になる。年報の令和7年度は486となっているが、令和6年度は485である。②所得第1〜3段階の割合は、1,094人÷3,443人で31.8％である。**第2章1の人口（見える化の将来推計・暦年）と第2章6の被保険者数（第10期将来推計用推計人口・年度）が別系列であることを注記した。**従前の注は「保険料算定との整合のため見える化の推計を用いる」と書いていたが、保険料算定は後者を用いており誤りであった</t>
+          <t>**足りない図6件のうち、10月4日に要介護度の維持・改善を作成し、残りは2件になった。****いずれも町データ待ちである。**地域ケア会議の開催回数・検討件数（町の事業実績待ち）と、介護給付適正化の主要3事業の実施状況（町の実施報告待ち）</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="19" t="inlineStr">
         <is>
-          <t>P11 品質・進捗管理</t>
+          <t>P9 意見聴取</t>
         </is>
       </c>
       <c r="B73" s="20" t="inlineStr">
         <is>
-          <t>11-2</t>
+          <t>9-3</t>
         </is>
       </c>
       <c r="C73" s="19" t="inlineStr">
         <is>
-          <t>図表データ管理台帳の整備と運用</t>
+          <t>協議会 第2回（骨子案・見込量・保険料・成果指標）</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E73" s="20" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="F73" s="20" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="G73" s="23" t="inlineStr">
@@ -8024,16 +8024,16 @@
         </is>
       </c>
       <c r="H73" s="32" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="I73" s="32" t="n">
-        <v>28.3</v>
+        <v>0</v>
       </c>
       <c r="J73" s="32" t="n">
-        <v>56.7</v>
+        <v>60</v>
       </c>
       <c r="K73" s="20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L73" s="33" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="M73" s="19" t="inlineStr">
         <is>
-          <t>**足りない図6件のうち、10月4日に要介護度の維持・改善を作成し、残りは2件になった。****いずれも町データ待ちである。**地域ケア会議の開催回数・検討件数（町の事業実績待ち）と、介護給付適正化の主要3事業の実施状況（町の実施報告待ち）</t>
+          <t>開催日の確定（案Aなら11月27日が期限）</t>
         </is>
       </c>
     </row>
@@ -8260,13 +8260,13 @@
         </is>
       </c>
       <c r="H77" s="32" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I77" s="32" t="n">
         <v>0</v>
       </c>
       <c r="J77" s="32" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K77" s="20" t="n">
         <v>4</v>
@@ -8344,7 +8344,7 @@
     <row r="80">
       <c r="A80" s="34" t="inlineStr">
         <is>
-          <t>加重の実績進捗率 72.2％　対　予定進捗率 63.7％　乖離 +8.5ポイント</t>
+          <t>加重の実績進捗率 74.0％　対　予定進捗率 63.7％　乖離 +10.3ポイント</t>
         </is>
       </c>
     </row>
@@ -8365,14 +8365,14 @@
     <row r="83">
       <c r="A83" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">　おおむね予定どおり 51件</t>
+          <t xml:space="preserve">　おおむね予定どおり 49件</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">　前倒し 17件</t>
+          <t xml:space="preserve">　前倒し 19件</t>
         </is>
       </c>
     </row>
@@ -9617,20 +9617,20 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K15" s="26" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
+      <c r="K15" s="23" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="L15" s="22" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="M15" s="23" t="n">
         <v>3</v>
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>**見える化は通いの場がR2まで、総合事業はR1・R2のみで値もほぼ空。**F7〜F14は本町の値が未登録。**9月28日に受領した国の（改修版）総合事業ワークシートにより、本町に訪問型サービスB・通所型サービスB（住民主体）の担い手が各1団体あることが分かった（訪問型A・通所型Aは実施していない）。**国の実施状況調査で令和元年度〜令和3年度に「実施の有無＝有」と回答され、市町村内の事業所数は平成29年度から令和4年度まで各1で一貫している。**ただし令和4年度以降の実施の有無は無回答で、令和5年度の利用者数は訪問型B 24人・通所型B 0人である**</t>
+          <t>**10月22日、総合事業の利用件数（令和6・7年度）と75歳以上人口の推計から、介護予防事業対象者数の見込み（令和9〜11年度）を素案 第16版に入れた。基本チェックリストの実施数は町データ待ち。****見える化は通いの場がR2まで、総合事業はR1・R2のみで値もほぼ空。**F7〜F14は本町の値が未登録。**9月28日に受領した国の（改修版）総合事業ワークシートにより、本町に訪問型サービスB・通所型サービスB（住民主体）の担い手が各1団体あることが分かった（訪問型A・通所型Aは実施していない）。**国の実施状況調査で令和元年度〜令和3年度に「実施の有無＝有」と回答され、市町村内の事業所数は平成29年度から令和4年度まで各1で一貫している。**ただし令和4年度以降の実施の有無は無回答で、令和5年度の利用者数は訪問型B 24人・通所型B 0人である**</t>
         </is>
       </c>
       <c r="O15" s="19" t="inlineStr">
@@ -10273,14 +10273,14 @@
         </is>
       </c>
       <c r="L23" s="22" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="M23" s="23" t="n">
         <v>5</v>
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>**第5版（8章・44表・約29,500字）。**第9期計画との対比、施策体系との対応、認定者数20期系列と年齢階層別分解、令和7年度調査による検証まで整理</t>
+          <t>**10月22日、第6版を作成。第8章「制度改正等の影響と介護保険財政の見通し」（報酬改定・負担割合の感度、基金の取崩し3案、施設整備ケース）を加えた。****第5版（8章・44表・約29,500字）。**第9期計画との対比、施策体系との対応、認定者数20期系列と年齢階層別分解、令和7年度調査による検証まで整理</t>
         </is>
       </c>
       <c r="O23" s="19" t="inlineStr">
@@ -10429,7 +10429,7 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="K25" s="27" t="inlineStr">
+      <c r="K25" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -10834,7 +10834,7 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K30" s="26" t="inlineStr">
+      <c r="K30" s="27" t="inlineStr">
         <is>
           <t>データ待ち</t>
         </is>
@@ -11159,20 +11159,20 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K34" s="27" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K34" s="23" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="L34" s="22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M34" s="23" t="n">
         <v>1</v>
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**10月22日、施設整備の2ケース（地域密着型特養1ユニット10人・GH1ユニット9人、令和10年4月開設）の給付費と保険料への影響を算定し、素案・見込量報告書・協議会資料に入れた。整備方針は町の判断待ち。**</t>
         </is>
       </c>
       <c r="O34" s="19" t="inlineStr">
@@ -11247,14 +11247,14 @@
         </is>
       </c>
       <c r="L35" s="22" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="M35" s="23" t="n">
         <v>4</v>
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>**第3版（13表・9,241字）。**第9期の5章構成・3基本目標・14施策を反映し、地域福祉計画との重複を精査。第9期の見込みと実績の対比も収載</t>
+          <t>**10月22日、第5版（確定版）を作成。第3章・第6章の要約を加え、章立てを素案 第16版と一致させた。協議会での確認を経て確定する。****第3版（13表・9,241字）。**第9期の5章構成・3基本目標・14施策を反映し、地域福祉計画との重複を精査。第9期の見込みと実績の対比も収載</t>
         </is>
       </c>
       <c r="O35" s="19" t="inlineStr">
@@ -11323,7 +11323,7 @@
           <t>2026-11</t>
         </is>
       </c>
-      <c r="K36" s="27" t="inlineStr">
+      <c r="K36" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -11404,7 +11404,7 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="K37" s="27" t="inlineStr">
+      <c r="K37" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -12013,14 +12013,14 @@
         </is>
       </c>
       <c r="L44" s="22" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="M44" s="23" t="n">
         <v>4</v>
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>**サービス見込量の算定結果（04_算定・見込量・10章・11表）を作成した。**算定の方法、基準期間の置き方、サービス見込量、給付費と標準給付費、地域支援事業費、供給実現性（定員との突合）、保険料の試算、据え置いた前提と動く幅、町への確認事項までを収めている</t>
+          <t>**10月22日、施設整備ケースを加えて作り直した（取崩しなしの基準額6,048円）。****サービス見込量の算定結果（04_算定・見込量・10章・11表）を作成した。**算定の方法、基準期間の置き方、サービス見込量、給付費と標準給付費、地域支援事業費、供給実現性（定員との突合）、保険料の試算、据え置いた前提と動く幅、町への確認事項までを収めている</t>
         </is>
       </c>
       <c r="O44" s="19" t="inlineStr">
@@ -12088,7 +12088,7 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="K45" s="27" t="inlineStr">
+      <c r="K45" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -12169,7 +12169,7 @@
           <t>2026-11</t>
         </is>
       </c>
-      <c r="K46" s="26" t="inlineStr">
+      <c r="K46" s="27" t="inlineStr">
         <is>
           <t>データ待ち</t>
         </is>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>**第15版（令和8年10月21日・88頁）。第12〜15版で国資料・審議会資料との照合、介護SCR、見える化出力、基金残高を反映した。未確定185箇所。****第11版（6章＋資料編・127表・図5点・見出し53件・78頁）。****10月15日に、法定記載事項チェック（新設）が見つけた4件の欠落を埋めた。**第6章9「老人福祉事業の量の目標」を新設し（老人福祉法第20条の8第2項・義務）、第1章7に県の意見聴取（介護保険法第117条第14項）、第1章6(2)に実績評価の根拠条文（改正後第9項）を加えた。**法定記載事項21件はすべて○である。**未確定は163箇所（町データ待ち89／協議会で設定55／決定後に記載13／見える化出力待ち6）で、**受託者が算定すべきものは引き続き0件である。****第6版（5章＋資料編・84表・図3点）。****第4章④に「人材の供給制約からみた見込量の妥当性」と「見える化システムによる算定との突合」を加えた。****第4章 基本目標2に「⑦ 在宅医療・介護連携の推進」を新設し、国の評価指標が求める4つの場面（日常の療養支援・入退院支援・急変時の対応・看取り）ごとの目指すべき姿を掲げた。****基本目標3① の介護給付適正化の記述を、令和8年度交付金の実際の得点に合わせて書いた**（主要3事業は3つとも実施、医療情報との突合は全国上位1割。0点はケアプラン点検の実施割合だけ）。**項目別の得点そのものは計画本文には置かず、評価から読み取れる中身と協議会への報告手順のみを書いている。**12施策すべてに現状と課題・施策の方向・主な事業・成果指標を記載。**第2版の未確定158箇所のうち61箇所が解消し97箇所となった。**第2章6（被保険者数・認定者数の見込み）を第10期将来推計用推計人口で確定し、第4章③にサービス見込量・給付費・標準給付費・地域支援事業費の事業別内訳・保険料基準額を入れた。**第5版（9月25日）で令和8年度の置き方を自然体推計に改め、保険料基準額は月額6,402円から6,048円（切上げ6,100円）となった。****9月25日の再検証で、延ばし方を見える化システムの仕様にそろえた**（施設は利用者数一定、居住系・在宅は認定者数で延ばす。月額▲13円）。従前の方式による算定は比較のケースとして残している。**第5章2の進行管理に、保険者機能強化推進交付金等の評価結果を点検項目として加えた**（評価結果を外部の議論の場で検証すること自体が評価指標の要件であるため）</t>
+          <t>**第16版（令和8年10月22日・92頁）。施設整備ケース、介護予防事業対象者数の見込み、総合計画との対応表、関連計画（国土強靱化・DX推進を追加）、町内事業所一覧、介護人材の需要の目安を入れた。第9期計画・第3期地域福祉計画の論点を突き合わせ、漏れていた事業（お助けサービス、住宅改修助成、虐待防止・成年後見の体制、施設の災害対策など）を補った。未確定189箇所。**第15版（令和8年10月21日・88頁）。第12〜15版で国資料・審議会資料との照合、介護SCR、見える化出力、基金残高を反映した。**第11版（6章＋資料編・127表・図5点・見出し53件・78頁）。****10月15日に、法定記載事項チェック（新設）が見つけた4件の欠落を埋めた。**第6章9「老人福祉事業の量の目標」を新設し（老人福祉法第20条の8第2項・義務）、第1章7に県の意見聴取（介護保険法第117条第14項）、第1章6(2)に実績評価の根拠条文（改正後第9項）を加えた。**法定記載事項21件はすべて○である。**未確定は163箇所（町データ待ち89／協議会で設定55／決定後に記載13／見える化出力待ち6）で、**受託者が算定すべきものは引き続き0件である。****第6版（5章＋資料編・84表・図3点）。****第4章④に「人材の供給制約からみた見込量の妥当性」と「見える化システムによる算定との突合」を加えた。****第4章 基本目標2に「⑦ 在宅医療・介護連携の推進」を新設し、国の評価指標が求める4つの場面（日常の療養支援・入退院支援・急変時の対応・看取り）ごとの目指すべき姿を掲げた。****基本目標3① の介護給付適正化の記述を、令和8年度交付金の実際の得点に合わせて書いた**（主要3事業は3つとも実施、医療情報との突合は全国上位1割。0点はケアプラン点検の実施割合だけ）。**項目別の得点そのものは計画本文には置かず、評価から読み取れる中身と協議会への報告手順のみを書いている。**12施策すべてに現状と課題・施策の方向・主な事業・成果指標を記載。**第2版の未確定158箇所のうち61箇所が解消し97箇所となった。**第2章6（被保険者数・認定者数の見込み）を第10期将来推計用推計人口で確定し、第4章③にサービス見込量・給付費・標準給付費・地域支援事業費の事業別内訳・保険料基準額を入れた。**第5版（9月25日）で令和8年度の置き方を自然体推計に改め、保険料基準額は月額6,402円から6,048円（切上げ6,100円）となった。****9月25日の再検証で、延ばし方を見える化システムの仕様にそろえた**（施設は利用者数一定、居住系・在宅は認定者数で延ばす。月額▲13円）。従前の方式による算定は比較のケースとして残している。**第5章2の進行管理に、保険者機能強化推進交付金等の評価結果を点検項目として加えた**（評価結果を外部の議論の場で検証すること自体が評価指標の要件であるため）</t>
         </is>
       </c>
       <c r="O47" s="19" t="inlineStr">
@@ -12580,7 +12580,7 @@
           <t>2026-12</t>
         </is>
       </c>
-      <c r="K51" s="27" t="inlineStr">
+      <c r="K51" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -12661,7 +12661,7 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="K52" s="27" t="inlineStr">
+      <c r="K52" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -13153,14 +13153,14 @@
         </is>
       </c>
       <c r="L58" s="22" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="M58" s="23" t="n">
         <v>2</v>
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>**資料を作成済み（令和8年10月6日・08_協議会資料）。骨子案 第4版・見込量・保険料の2案・成果指標の目標値の置き方の3案。数値は算定モジュールから引いており、算定が変われば資料も変わる**</t>
+          <t>**10月22日、令和8年12月開催を前提に資料を更新し、次第（案）・当日の進め方・会議録（要旨）様式を作成した（障がいの自立支援協議会分も）。****資料を作成済み（令和8年10月6日・08_協議会資料）。骨子案 第4版・見込量・保険料の2案・成果指標の目標値の置き方の3案。数値は算定モジュールから引いており、算定が変われば資料も変わる**</t>
         </is>
       </c>
       <c r="O58" s="19" t="inlineStr">
@@ -13228,7 +13228,7 @@
           <t>2026-12</t>
         </is>
       </c>
-      <c r="K59" s="27" t="inlineStr">
+      <c r="K59" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -13390,7 +13390,7 @@
           <t>2027-01</t>
         </is>
       </c>
-      <c r="K61" s="27" t="inlineStr">
+      <c r="K61" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -13471,7 +13471,7 @@
           <t>2027-02</t>
         </is>
       </c>
-      <c r="K62" s="27" t="inlineStr">
+      <c r="K62" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -13552,7 +13552,7 @@
           <t>2027-02</t>
         </is>
       </c>
-      <c r="K63" s="27" t="inlineStr">
+      <c r="K63" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -13633,20 +13633,20 @@
           <t>2027-02</t>
         </is>
       </c>
-      <c r="K64" s="27" t="inlineStr">
+      <c r="K64" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
       <c r="L64" s="22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M64" s="23" t="n">
         <v>3</v>
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**10月22日、素案（92頁）を章ごとに数え、計画書80頁程度への頁配分計画を作成した（10_納品・印刷）。**</t>
         </is>
       </c>
       <c r="O64" s="19" t="inlineStr">
@@ -13714,7 +13714,7 @@
           <t>2027-02</t>
         </is>
       </c>
-      <c r="K65" s="27" t="inlineStr">
+      <c r="K65" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -13795,7 +13795,7 @@
           <t>2027-02</t>
         </is>
       </c>
-      <c r="K66" s="27" t="inlineStr">
+      <c r="K66" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -13957,7 +13957,7 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="K68" s="27" t="inlineStr">
+      <c r="K68" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -14039,7 +14039,7 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="K69" s="27" t="inlineStr">
+      <c r="K69" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -14120,7 +14120,7 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="K70" s="27" t="inlineStr">
+      <c r="K70" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -14201,7 +14201,7 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="K71" s="27" t="inlineStr">
+      <c r="K71" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -15765,7 +15765,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="E6" s="27" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -15805,7 +15805,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -16057,7 +16057,7 @@
           <t>受託者</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -16084,7 +16084,7 @@
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="D9" s="27" t="inlineStr">
+      <c r="D9" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -16111,7 +16111,7 @@
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="D10" s="27" t="inlineStr">
+      <c r="D10" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -16138,7 +16138,7 @@
           <t>町</t>
         </is>
       </c>
-      <c r="D11" s="27" t="inlineStr">
+      <c r="D11" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -16165,7 +16165,7 @@
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="D12" s="27" t="inlineStr">
+      <c r="D12" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -16192,7 +16192,7 @@
           <t>受託者</t>
         </is>
       </c>
-      <c r="D13" s="27" t="inlineStr">
+      <c r="D13" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -16529,7 +16529,7 @@
           <t>見える化システム</t>
         </is>
       </c>
-      <c r="D10" s="27" t="inlineStr">
+      <c r="D10" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -16913,7 +16913,7 @@
           <t>町</t>
         </is>
       </c>
-      <c r="D22" s="27" t="inlineStr">
+      <c r="D22" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -17267,7 +17267,7 @@
           <t>パブリックコメントの結果、計画最終案</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -17510,7 +17510,7 @@
           <t>町の事業実績（令和3〜7年度）で代替する（依頼票H3）</t>
         </is>
       </c>
-      <c r="F5" s="26" t="inlineStr">
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>データ待ち</t>
         </is>
@@ -17630,7 +17630,7 @@
           <t>整備の経緯を町に確認する（依頼票H15）</t>
         </is>
       </c>
-      <c r="F9" s="27" t="inlineStr">
+      <c r="F9" s="26" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -17840,7 +17840,7 @@
           <t>**町の総合事業上限額算定の手引き（平成27年度〜令和6年度）と地域支援事業交付金事業実績報告書の受領**</t>
         </is>
       </c>
-      <c r="F16" s="26" t="inlineStr">
+      <c r="F16" s="27" t="inlineStr">
         <is>
           <t>データ待ち</t>
         </is>
